--- a/data-manipulation-scripts/sheets-cleanup/sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -136,79 +136,7 @@
     <t>BOBINA IGNICAO ZOUIL CG150/ TITAN KS/ FAN ESI 2010 A 2012</t>
   </si>
   <si>
-    <t>7908305634063</t>
-  </si>
-  <si>
-    <t>BOBOBINA  PULSO MHX YES125 2005 A 2011/ INTRUDER125 2002 A 2016/ KATANA125 1996 A 1996</t>
-  </si>
-  <si>
-    <t>7908305618681</t>
-  </si>
-  <si>
-    <t>BOBOBINA  PULSO MHX CBX150 1990 A 1993/ CBX200 1994 A 2001/ BROS NXR150 1990 A 1993/XR200 1994 A 2002</t>
-  </si>
-  <si>
-    <t>7908305634186</t>
-  </si>
-  <si>
-    <t>BOBOBINA  PULSO MHX JET50 2014 A 2020/ HYPE50 2010 A 2014</t>
-  </si>
-  <si>
-    <t>7908305634100</t>
-  </si>
-  <si>
-    <t>BOBINA PULSO MHX FAZER250 2006 A 2019/ LANDER250 2007 A 2019/ TENERE 2011 A 2019</t>
-  </si>
-  <si>
-    <t>7908305635152</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO MHX YBR125K 2000 A 2001</t>
-  </si>
-  <si>
-    <t>7908305602505</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO MHX BOBINA IGNICAOZ100 DREAM</t>
-  </si>
-  <si>
-    <t>7908305634407</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO MHX CB300R 2010 A 2015/ XRE300 2010 A 2018/ TWISTER250 2001 A 2008/ TORNADO250 2001 A 2008</t>
-  </si>
-  <si>
-    <t>7908305634391</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO MHX FAZER150 ED 2014 A 2015/ FACTOR150 2016 A 2018/ XTZ CROSSER 2014 A 2018</t>
-  </si>
-  <si>
-    <t>7899468071010</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO JECPRO CG FAN TITAN150 2004/ BROS NXR150 2006</t>
-  </si>
-  <si>
-    <t>751320983534</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO IRON YBR 2000 A 2001 182327</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO MAGNETRON CG125</t>
-  </si>
-  <si>
-    <t>BOBINA  PULSO MAGNETRON CG TITAN FAN 2003 A 2004</t>
-  </si>
-  <si>
-    <t>7898485612213</t>
-  </si>
-  <si>
-    <t>BOBINA  LUZ MAGNETRON BOBINA IGNICAOZ DREAM</t>
-  </si>
-  <si>
-    <t>BOBINA  LUZ MAGNETRON CG125</t>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -762,7 +690,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -793,166 +721,76 @@
       <c r="D25" s="3"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D26" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D27" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D28" s="2">
-        <v>3.0</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D29" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D30" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D31" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D32" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D33" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D34" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="4"/>
-      <c r="B36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D36" s="2">
-        <v>40.0</v>
-      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="4"/>
-      <c r="B37" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D37" s="2">
-        <v>38.0</v>
-      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="4"/>
@@ -967,28 +805,16 @@
       <c r="D39" s="3"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
       <c r="D40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="4"/>
-      <c r="B41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D41" s="2">
-        <v>50.0</v>
-      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="4"/>
@@ -6696,98 +6522,14 @@
       <c r="C992" s="3"/>
       <c r="D992" s="3"/>
     </row>
-    <row r="993">
-      <c r="A993" s="4"/>
-      <c r="B993" s="3"/>
-      <c r="C993" s="3"/>
-      <c r="D993" s="3"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="4"/>
-      <c r="B994" s="3"/>
-      <c r="C994" s="3"/>
-      <c r="D994" s="3"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="4"/>
-      <c r="B995" s="3"/>
-      <c r="C995" s="3"/>
-      <c r="D995" s="3"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="4"/>
-      <c r="B996" s="3"/>
-      <c r="C996" s="3"/>
-      <c r="D996" s="3"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="4"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="4"/>
-      <c r="B998" s="3"/>
-      <c r="C998" s="3"/>
-      <c r="D998" s="3"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="4"/>
-      <c r="B999" s="3"/>
-      <c r="C999" s="3"/>
-      <c r="D999" s="3"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
-    <row r="1001">
-      <c r="A1001" s="4"/>
-      <c r="B1001" s="3"/>
-      <c r="C1001" s="3"/>
-      <c r="D1001" s="3"/>
-    </row>
-    <row r="1002">
-      <c r="A1002" s="4"/>
-      <c r="B1002" s="3"/>
-      <c r="C1002" s="3"/>
-      <c r="D1002" s="3"/>
-    </row>
-    <row r="1003">
-      <c r="A1003" s="4"/>
-      <c r="B1003" s="3"/>
-      <c r="C1003" s="3"/>
-      <c r="D1003" s="3"/>
-    </row>
-    <row r="1004">
-      <c r="A1004" s="4"/>
-      <c r="B1004" s="3"/>
-      <c r="C1004" s="3"/>
-      <c r="D1004" s="3"/>
-    </row>
-    <row r="1005">
-      <c r="A1005" s="4"/>
-      <c r="B1005" s="3"/>
-      <c r="C1005" s="3"/>
-      <c r="D1005" s="3"/>
-    </row>
-    <row r="1006">
-      <c r="A1006" s="4"/>
-      <c r="B1006" s="3"/>
-      <c r="C1006" s="3"/>
-      <c r="D1006" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1006">
+  <conditionalFormatting sqref="A1:A992">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1006">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A992">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BOBINA IGNICAO E  PULSO 03_02.xlsx
@@ -596,7 +596,9 @@
       <c r="C13" s="2">
         <v>1.0</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2">
+        <v>183.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -622,7 +624,9 @@
       <c r="C15" s="2">
         <v>2.0</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2">
+        <v>75.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
@@ -632,7 +636,9 @@
       <c r="C16" s="2">
         <v>3.0</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="2">
+        <v>70.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
@@ -686,7 +692,9 @@
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="2">
+        <v>158.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
